--- a/Content/ProjectVD/DataTable/EnemyStatsInfo.xlsx
+++ b/Content/ProjectVD/DataTable/EnemyStatsInfo.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\thunderfury\ProjectVD\Content\ProjectVD\DataTable\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D1B12335-6626-47AF-9A5A-C8D37E820102}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B05E7C5-B6E7-4700-A766-91CD1282BA48}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12648" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
   <si>
     <t>Name</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -64,6 +64,10 @@
   </si>
   <si>
     <t>PatrolRange</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>MaxMovementSpeed</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -389,13 +393,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I2"/>
+  <dimension ref="A1:J2"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="7" max="7" width="39" customWidth="1"/>
+    <col min="8" max="8" width="22.796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -423,8 +428,11 @@
       <c r="I1" t="s">
         <v>8</v>
       </c>
+      <c r="J1" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -451,6 +459,9 @@
       </c>
       <c r="I2">
         <v>3</v>
+      </c>
+      <c r="J2">
+        <v>1000</v>
       </c>
     </row>
   </sheetData>

--- a/Content/ProjectVD/DataTable/EnemyStatsInfo.xlsx
+++ b/Content/ProjectVD/DataTable/EnemyStatsInfo.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\thunderfury\ProjectVD\Content\ProjectVD\DataTable\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B05E7C5-B6E7-4700-A766-91CD1282BA48}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C3BDCE8-2880-4747-9EEF-1734C3142D61}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12648" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
   <si>
     <t>Name</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -68,6 +68,10 @@
   </si>
   <si>
     <t>MaxMovementSpeed</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SkeletonMarauder</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -393,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J2"/>
+  <dimension ref="A1:J3"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="7" max="7" width="39" customWidth="1"/>
@@ -464,6 +468,38 @@
         <v>1000</v>
       </c>
     </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B3">
+        <v>100</v>
+      </c>
+      <c r="C3">
+        <v>5</v>
+      </c>
+      <c r="D3">
+        <v>1</v>
+      </c>
+      <c r="E3">
+        <v>300</v>
+      </c>
+      <c r="F3">
+        <v>500</v>
+      </c>
+      <c r="G3">
+        <v>2.5</v>
+      </c>
+      <c r="H3">
+        <v>100</v>
+      </c>
+      <c r="I3">
+        <v>3</v>
+      </c>
+      <c r="J3">
+        <v>200</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Content/ProjectVD/DataTable/EnemyStatsInfo.xlsx
+++ b/Content/ProjectVD/DataTable/EnemyStatsInfo.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\thunderfury\ProjectVD\Content\ProjectVD\DataTable\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C3BDCE8-2880-4747-9EEF-1734C3142D61}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{71D4828C-19CF-4FC8-A63C-E02ECAEEF5EC}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12648" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
   <si>
     <t>Name</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -72,6 +72,10 @@
   </si>
   <si>
     <t>SkeletonMarauder</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>GothicKnight</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -397,7 +401,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J3"/>
+  <dimension ref="A1:J4"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="7" max="7" width="39" customWidth="1"/>
@@ -500,6 +504,38 @@
         <v>200</v>
       </c>
     </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B4">
+        <v>750</v>
+      </c>
+      <c r="C4">
+        <v>10</v>
+      </c>
+      <c r="D4">
+        <v>1</v>
+      </c>
+      <c r="E4">
+        <v>450</v>
+      </c>
+      <c r="F4">
+        <v>1000</v>
+      </c>
+      <c r="G4">
+        <v>0</v>
+      </c>
+      <c r="H4">
+        <v>0</v>
+      </c>
+      <c r="I4">
+        <v>3</v>
+      </c>
+      <c r="J4">
+        <v>75</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Content/ProjectVD/DataTable/EnemyStatsInfo.xlsx
+++ b/Content/ProjectVD/DataTable/EnemyStatsInfo.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\thunderfury\ProjectVD\Content\ProjectVD\DataTable\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{71D4828C-19CF-4FC8-A63C-E02ECAEEF5EC}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{41019CEA-3B75-4C8F-B44C-2320BC9DA775}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12648" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -527,7 +527,7 @@
         <v>0</v>
       </c>
       <c r="H4">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="I4">
         <v>3</v>

--- a/Content/ProjectVD/DataTable/EnemyStatsInfo.xlsx
+++ b/Content/ProjectVD/DataTable/EnemyStatsInfo.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\thunderfury\ProjectVD\Content\ProjectVD\DataTable\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{41019CEA-3B75-4C8F-B44C-2320BC9DA775}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F6C59D84-06BE-487D-9D07-F8A6B3C144D1}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12648" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
   <si>
     <t>Name</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -67,16 +67,18 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>MaxMovementSpeed</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>SkeletonMarauder</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>GothicKnight</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>MaxPatrolMoveSpeed</t>
+  </si>
+  <si>
+    <t>MaxChaseMoveSpeed</t>
   </si>
 </sst>
 </file>
@@ -401,14 +403,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J4"/>
+  <dimension ref="A1:K4"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="7" max="7" width="39" customWidth="1"/>
     <col min="8" max="8" width="22.796875" customWidth="1"/>
+    <col min="9" max="9" width="20" customWidth="1"/>
+    <col min="10" max="10" width="9.296875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -437,10 +441,13 @@
         <v>8</v>
       </c>
       <c r="J1" t="s">
-        <v>10</v>
+        <v>12</v>
+      </c>
+      <c r="K1" t="s">
+        <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -471,10 +478,13 @@
       <c r="J2">
         <v>1000</v>
       </c>
+      <c r="K2">
+        <v>1000</v>
+      </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B3">
         <v>100</v>
@@ -503,10 +513,13 @@
       <c r="J3">
         <v>200</v>
       </c>
+      <c r="K3">
+        <v>200</v>
+      </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B4">
         <v>750</v>
@@ -534,6 +547,9 @@
       </c>
       <c r="J4">
         <v>75</v>
+      </c>
+      <c r="K4">
+        <v>150</v>
       </c>
     </row>
   </sheetData>
